--- a/business_surveys/036_entrepreneurship_stabilization_survey--business_surveys.xlsx
+++ b/business_surveys/036_entrepreneurship_stabilization_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frequency of Business Stabilization Survey</t>
+          <t>Business Stabilization Survey Survey Frequency</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_participants_type</t>
+          <t>business_stabilization_survey_participants_type_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Type of Participants in Business Stabilization Survey</t>
+          <t>Business Stabilization Survey Participants Type 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_purpose</t>
+          <t>business_stabilization_survey_purpose_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Purpose of Business Stabilization Survey</t>
+          <t>Business Stabilization Survey Purpose 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_impact</t>
+          <t>business_stabilization_survey_impact_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Impact of Business Stabilization Survey</t>
+          <t>Business Stabilization Survey Impact 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_purpose</t>
+          <t>business_stabilization_survey_purpose_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Purpose of Business Stabilization Survey</t>
+          <t>Business Stabilization Survey Purpose 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_participants_type_choices</t>
+          <t>business_stabilization_survey_participants_type_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_participants_type_choices</t>
+          <t>business_stabilization_survey_participants_type_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_purpose_choices</t>
+          <t>business_stabilization_survey_purpose_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_purpose_choices</t>
+          <t>business_stabilization_survey_purpose_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_impact_choices</t>
+          <t>business_stabilization_survey_impact_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_impact_choices</t>
+          <t>business_stabilization_survey_impact_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_purpose_choices</t>
+          <t>business_stabilization_survey_purpose_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>business_stabilization_survey_purpose_choices</t>
+          <t>business_stabilization_survey_purpose_3_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
